--- a/data/nzd0168/nzd0168.xlsx
+++ b/data/nzd0168/nzd0168.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G374"/>
+  <dimension ref="A1:G375"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10524,6 +10524,33 @@
       <c r="G374" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:05:44+00:00</t>
+        </is>
+      </c>
+      <c r="B375" t="n">
+        <v>354.62</v>
+      </c>
+      <c r="C375" t="n">
+        <v>355.86</v>
+      </c>
+      <c r="D375" t="n">
+        <v>362.78</v>
+      </c>
+      <c r="E375" t="n">
+        <v>355.61</v>
+      </c>
+      <c r="F375" t="n">
+        <v>373.15</v>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -10538,7 +10565,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B391"/>
+  <dimension ref="A1:B393"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14451,6 +14478,26 @@
       </c>
       <c r="B391" t="n">
         <v>-0.4</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>2026-01-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B392" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B393" t="n">
+        <v>0.52</v>
       </c>
     </row>
   </sheetData>
@@ -14619,28 +14666,28 @@
         <v>0.055</v>
       </c>
       <c r="I2" t="n">
-        <v>0.09469293036156078</v>
+        <v>0.09456430092090176</v>
       </c>
       <c r="J2" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="K2" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01757055490724146</v>
+        <v>0.01762506147128085</v>
       </c>
       <c r="M2" t="n">
-        <v>3.960170395570287</v>
+        <v>3.950303646092948</v>
       </c>
       <c r="N2" t="n">
-        <v>27.03344526598929</v>
+        <v>26.96131516534532</v>
       </c>
       <c r="O2" t="n">
-        <v>5.199369698914407</v>
+        <v>5.192428638445146</v>
       </c>
       <c r="P2" t="n">
-        <v>352.351807534142</v>
+        <v>352.3531751576369</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -14697,28 +14744,28 @@
         <v>0.0852</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1550853356039571</v>
+        <v>0.158941861371877</v>
       </c>
       <c r="J3" t="n">
+        <v>374</v>
+      </c>
+      <c r="K3" t="n">
         <v>373</v>
       </c>
-      <c r="K3" t="n">
-        <v>372</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.04728971711902163</v>
+        <v>0.04958595886996087</v>
       </c>
       <c r="M3" t="n">
-        <v>4.024020270993167</v>
+        <v>4.02573528281909</v>
       </c>
       <c r="N3" t="n">
-        <v>25.88008086024596</v>
+        <v>25.94529606623763</v>
       </c>
       <c r="O3" t="n">
-        <v>5.087246884145291</v>
+        <v>5.093652527041634</v>
       </c>
       <c r="P3" t="n">
-        <v>344.6371998445956</v>
+        <v>344.5959274560426</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -14775,28 +14822,28 @@
         <v>0.08119999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1955491479323474</v>
+        <v>0.2022167578785056</v>
       </c>
       <c r="J4" t="n">
+        <v>374</v>
+      </c>
+      <c r="K4" t="n">
         <v>373</v>
       </c>
-      <c r="K4" t="n">
-        <v>372</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.05318553778462864</v>
+        <v>0.05639161758508715</v>
       </c>
       <c r="M4" t="n">
-        <v>4.733758551910813</v>
+        <v>4.753231714371696</v>
       </c>
       <c r="N4" t="n">
-        <v>36.3591069733507</v>
+        <v>36.66396565373189</v>
       </c>
       <c r="O4" t="n">
-        <v>6.029851322657193</v>
+        <v>6.055077675284759</v>
       </c>
       <c r="P4" t="n">
-        <v>345.3011836639805</v>
+        <v>345.2298271620463</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -14853,28 +14900,28 @@
         <v>0.1843</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2075557257836243</v>
+        <v>0.2129746498588265</v>
       </c>
       <c r="J5" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="K5" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05234004369227063</v>
+        <v>0.05492921366282399</v>
       </c>
       <c r="M5" t="n">
-        <v>5.257643659164877</v>
+        <v>5.270430161914792</v>
       </c>
       <c r="N5" t="n">
-        <v>42.05699879198666</v>
+        <v>42.21402750434552</v>
       </c>
       <c r="O5" t="n">
-        <v>6.48513675969803</v>
+        <v>6.497232295704496</v>
       </c>
       <c r="P5" t="n">
-        <v>340.0290801267492</v>
+        <v>339.9714646396261</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -14931,28 +14978,28 @@
         <v>0.0422</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1910578219643618</v>
+        <v>-0.1836611212477405</v>
       </c>
       <c r="J6" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="K6" t="n">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="L6" t="n">
-        <v>0.004913329853192594</v>
+        <v>0.004563056234177632</v>
       </c>
       <c r="M6" t="n">
-        <v>15.03489286639272</v>
+        <v>15.03695853788941</v>
       </c>
       <c r="N6" t="n">
-        <v>390.9823967299151</v>
+        <v>390.4152956618702</v>
       </c>
       <c r="O6" t="n">
-        <v>19.77327481045856</v>
+        <v>19.75892951710366</v>
       </c>
       <c r="P6" t="n">
-        <v>364.6918030404818</v>
+        <v>364.6119225554418</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -14990,7 +15037,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G374"/>
+  <dimension ref="A1:G375"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28807,6 +28854,43 @@
         </is>
       </c>
     </row>
+    <row r="375">
+      <c r="A375" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:05:44+00:00</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>-36.76833580342324,175.7497028686367</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>-36.76903637752293,175.74948756872587</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>-36.76975617609675,175.74942425039876</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>-36.77046692623343,175.74923802941066</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>-36.77116190725569,175.74946017665633</t>
+        </is>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0168/nzd0168.xlsx
+++ b/data/nzd0168/nzd0168.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G375"/>
+  <dimension ref="A1:G376"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10551,6 +10551,33 @@
       <c r="G375" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-02 22:05:53+00:00</t>
+        </is>
+      </c>
+      <c r="B376" t="n">
+        <v>351.86</v>
+      </c>
+      <c r="C376" t="n">
+        <v>356.27</v>
+      </c>
+      <c r="D376" t="n">
+        <v>362.95</v>
+      </c>
+      <c r="E376" t="n">
+        <v>356.32</v>
+      </c>
+      <c r="F376" t="n">
+        <v>377.58</v>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -10565,7 +10592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B393"/>
+  <dimension ref="A1:B394"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14498,6 +14525,16 @@
       </c>
       <c r="B393" t="n">
         <v>0.52</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>2026-02-02 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B394" t="n">
+        <v>0.32</v>
       </c>
     </row>
   </sheetData>
@@ -14666,28 +14703,28 @@
         <v>0.055</v>
       </c>
       <c r="I2" t="n">
-        <v>0.09456430092090176</v>
+        <v>0.09295637671981924</v>
       </c>
       <c r="J2" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="K2" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01762506147128085</v>
+        <v>0.01712482740871546</v>
       </c>
       <c r="M2" t="n">
-        <v>3.950303646092948</v>
+        <v>3.948721588275655</v>
       </c>
       <c r="N2" t="n">
-        <v>26.96131516534532</v>
+        <v>26.91320145595668</v>
       </c>
       <c r="O2" t="n">
-        <v>5.192428638445146</v>
+        <v>5.187793505523969</v>
       </c>
       <c r="P2" t="n">
-        <v>352.3531751576369</v>
+        <v>352.3703190967374</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -14744,28 +14781,28 @@
         <v>0.0852</v>
       </c>
       <c r="I3" t="n">
-        <v>0.158941861371877</v>
+        <v>0.162971032887135</v>
       </c>
       <c r="J3" t="n">
+        <v>375</v>
+      </c>
+      <c r="K3" t="n">
         <v>374</v>
       </c>
-      <c r="K3" t="n">
-        <v>373</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.04958595886996087</v>
+        <v>0.05201092500527682</v>
       </c>
       <c r="M3" t="n">
-        <v>4.02573528281909</v>
+        <v>4.02803163721205</v>
       </c>
       <c r="N3" t="n">
-        <v>25.94529606623763</v>
+        <v>26.02319641996721</v>
       </c>
       <c r="O3" t="n">
-        <v>5.093652527041634</v>
+        <v>5.101293602603874</v>
       </c>
       <c r="P3" t="n">
-        <v>344.5959274560426</v>
+        <v>344.552687234005</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -14822,28 +14859,28 @@
         <v>0.08119999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2022167578785056</v>
+        <v>0.208895506438333</v>
       </c>
       <c r="J4" t="n">
+        <v>375</v>
+      </c>
+      <c r="K4" t="n">
         <v>374</v>
       </c>
-      <c r="K4" t="n">
-        <v>373</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.05639161758508715</v>
+        <v>0.05966446720115859</v>
       </c>
       <c r="M4" t="n">
-        <v>4.753231714371696</v>
+        <v>4.77297477140243</v>
       </c>
       <c r="N4" t="n">
-        <v>36.66396565373189</v>
+        <v>36.97058523034791</v>
       </c>
       <c r="O4" t="n">
-        <v>6.055077675284759</v>
+        <v>6.080344170386074</v>
       </c>
       <c r="P4" t="n">
-        <v>345.2298271620463</v>
+        <v>345.1581522359315</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -14900,28 +14937,28 @@
         <v>0.1843</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2129746498588265</v>
+        <v>0.2187068021062789</v>
       </c>
       <c r="J5" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="K5" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05492921366282399</v>
+        <v>0.05768359089390274</v>
       </c>
       <c r="M5" t="n">
-        <v>5.270430161914792</v>
+        <v>5.284991272166358</v>
       </c>
       <c r="N5" t="n">
-        <v>42.21402750434552</v>
+        <v>42.40371164259476</v>
       </c>
       <c r="O5" t="n">
-        <v>6.497232295704496</v>
+        <v>6.511813237693074</v>
       </c>
       <c r="P5" t="n">
-        <v>339.9714646396261</v>
+        <v>339.9103475366066</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -14978,28 +15015,28 @@
         <v>0.0422</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1836611212477405</v>
+        <v>-0.1739217591305237</v>
       </c>
       <c r="J6" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="K6" t="n">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="L6" t="n">
-        <v>0.004563056234177632</v>
+        <v>0.004109118587559357</v>
       </c>
       <c r="M6" t="n">
-        <v>15.03695853788941</v>
+        <v>15.0521222053069</v>
       </c>
       <c r="N6" t="n">
-        <v>390.4152956618702</v>
+        <v>390.2138045942615</v>
       </c>
       <c r="O6" t="n">
-        <v>19.75892951710366</v>
+        <v>19.75383012466852</v>
       </c>
       <c r="P6" t="n">
-        <v>364.6119225554418</v>
+        <v>364.5064500865747</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -15037,7 +15074,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G375"/>
+  <dimension ref="A1:G376"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28891,6 +28928,43 @@
         </is>
       </c>
     </row>
+    <row r="376">
+      <c r="A376" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-02 22:05:53+00:00</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>-36.768329964691134,175.7496728298249</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>-36.769037063409094,175.74949207958355</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>-36.769756355432364,175.74942614078643</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>-36.770467089452225,175.74924597674521</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>-36.77115994035012,175.74950971985348</t>
+        </is>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0168/nzd0168.xlsx
+++ b/data/nzd0168/nzd0168.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G376"/>
+  <dimension ref="A1:G378"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10576,6 +10576,60 @@
         <v>377.58</v>
       </c>
       <c r="G376" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:05:37+00:00</t>
+        </is>
+      </c>
+      <c r="B377" t="n">
+        <v>351.67</v>
+      </c>
+      <c r="C377" t="n">
+        <v>356.22</v>
+      </c>
+      <c r="D377" t="n">
+        <v>362.67</v>
+      </c>
+      <c r="E377" t="n">
+        <v>355.01</v>
+      </c>
+      <c r="F377" t="n">
+        <v>381.88</v>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:06:08+00:00</t>
+        </is>
+      </c>
+      <c r="B378" t="n">
+        <v>354.74</v>
+      </c>
+      <c r="C378" t="n">
+        <v>356.71</v>
+      </c>
+      <c r="D378" t="n">
+        <v>363.86</v>
+      </c>
+      <c r="E378" t="n">
+        <v>354.36</v>
+      </c>
+      <c r="F378" t="n">
+        <v>380.1</v>
+      </c>
+      <c r="G378" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -10592,7 +10646,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B394"/>
+  <dimension ref="A1:B396"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14535,6 +14589,26 @@
       </c>
       <c r="B394" t="n">
         <v>0.32</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B395" t="n">
+        <v>-0.42</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B396" t="n">
+        <v>0.78</v>
       </c>
     </row>
   </sheetData>
@@ -14703,28 +14777,28 @@
         <v>0.055</v>
       </c>
       <c r="I2" t="n">
-        <v>0.09295637671981924</v>
+        <v>0.09121729101912245</v>
       </c>
       <c r="J2" t="n">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="K2" t="n">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01712482740871546</v>
+        <v>0.01667578309270812</v>
       </c>
       <c r="M2" t="n">
-        <v>3.948721588275655</v>
+        <v>3.937352064507215</v>
       </c>
       <c r="N2" t="n">
-        <v>26.91320145595668</v>
+        <v>26.79688370677278</v>
       </c>
       <c r="O2" t="n">
-        <v>5.187793505523969</v>
+        <v>5.176570651191073</v>
       </c>
       <c r="P2" t="n">
-        <v>352.3703190967374</v>
+        <v>352.3889137194637</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -14781,28 +14855,28 @@
         <v>0.0852</v>
       </c>
       <c r="I3" t="n">
-        <v>0.162971032887135</v>
+        <v>0.1710736942664515</v>
       </c>
       <c r="J3" t="n">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="K3" t="n">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05201092500527682</v>
+        <v>0.05702316732935364</v>
       </c>
       <c r="M3" t="n">
-        <v>4.02803163721205</v>
+        <v>4.033599380284457</v>
       </c>
       <c r="N3" t="n">
-        <v>26.02319641996721</v>
+        <v>26.18474883501023</v>
       </c>
       <c r="O3" t="n">
-        <v>5.101293602603874</v>
+        <v>5.117103559144589</v>
       </c>
       <c r="P3" t="n">
-        <v>344.552687234005</v>
+        <v>344.4654491648377</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -14859,28 +14933,28 @@
         <v>0.08119999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.208895506438333</v>
+        <v>0.2223242357556038</v>
       </c>
       <c r="J4" t="n">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="K4" t="n">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05966446720115859</v>
+        <v>0.06640341432738595</v>
       </c>
       <c r="M4" t="n">
-        <v>4.77297477140243</v>
+        <v>4.812921924276665</v>
       </c>
       <c r="N4" t="n">
-        <v>36.97058523034791</v>
+        <v>37.59886357030088</v>
       </c>
       <c r="O4" t="n">
-        <v>6.080344170386074</v>
+        <v>6.131791220377687</v>
       </c>
       <c r="P4" t="n">
-        <v>345.1581522359315</v>
+        <v>345.0135695307458</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -14937,28 +15011,28 @@
         <v>0.1843</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2187068021062789</v>
+        <v>0.2282106727152822</v>
       </c>
       <c r="J5" t="n">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="K5" t="n">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05768359089390274</v>
+        <v>0.06259443001717435</v>
       </c>
       <c r="M5" t="n">
-        <v>5.284991272166358</v>
+        <v>5.304739528806116</v>
       </c>
       <c r="N5" t="n">
-        <v>42.40371164259476</v>
+        <v>42.59741022483987</v>
       </c>
       <c r="O5" t="n">
-        <v>6.511813237693074</v>
+        <v>6.52666915239618</v>
       </c>
       <c r="P5" t="n">
-        <v>339.9103475366066</v>
+        <v>339.8086876688735</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -15015,28 +15089,28 @@
         <v>0.0422</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1739217591305237</v>
+        <v>-0.151106167928276</v>
       </c>
       <c r="J6" t="n">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="K6" t="n">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="L6" t="n">
-        <v>0.004109118587559357</v>
+        <v>0.003122727866169406</v>
       </c>
       <c r="M6" t="n">
-        <v>15.0521222053069</v>
+        <v>15.10417033632293</v>
       </c>
       <c r="N6" t="n">
-        <v>390.2138045942615</v>
+        <v>390.4752257664189</v>
       </c>
       <c r="O6" t="n">
-        <v>19.75383012466852</v>
+        <v>19.76044599108074</v>
       </c>
       <c r="P6" t="n">
-        <v>364.5064500865747</v>
+        <v>364.2585776855964</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -15074,7 +15148,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G376"/>
+  <dimension ref="A1:G378"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28965,6 +29039,80 @@
         </is>
       </c>
     </row>
+    <row r="377">
+      <c r="A377" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:05:37+00:00</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>-36.76832956274912,175.74967076193582</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>-36.76903697976446,175.74949152947895</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>-36.76975606005603,175.74942302720675</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>-36.77046678830164,175.7492313133533</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>-36.77115803114447,175.74955780918336</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:06:08+00:00</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>-36.76833605728098,175.74970417467205</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>-36.769037799481865,175.74949692050407</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>-36.76975731540485,175.7494362599205</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>-36.77046663887512,175.7492240376245</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>-36.77115882146916,175.74953790243794</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0168/nzd0168.xlsx
+++ b/data/nzd0168/nzd0168.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G378"/>
+  <dimension ref="A1:G379"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10632,6 +10632,33 @@
       <c r="G378" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-14 22:05:26+00:00</t>
+        </is>
+      </c>
+      <c r="B379" t="n">
+        <v>353.73</v>
+      </c>
+      <c r="C379" t="n">
+        <v>355.13</v>
+      </c>
+      <c r="D379" t="n">
+        <v>361.51</v>
+      </c>
+      <c r="E379" t="n">
+        <v>352.75</v>
+      </c>
+      <c r="F379" t="n">
+        <v>373.9</v>
+      </c>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B396"/>
+  <dimension ref="A1:B397"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14609,6 +14636,16 @@
       </c>
       <c r="B396" t="n">
         <v>0.78</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>2026-03-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B397" t="n">
+        <v>-0.42</v>
       </c>
     </row>
   </sheetData>
@@ -14777,28 +14814,28 @@
         <v>0.055</v>
       </c>
       <c r="I2" t="n">
-        <v>0.09121729101912245</v>
+        <v>0.09063973406783112</v>
       </c>
       <c r="J2" t="n">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="K2" t="n">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01667578309270812</v>
+        <v>0.01656109086280277</v>
       </c>
       <c r="M2" t="n">
-        <v>3.937352064507215</v>
+        <v>3.93009710910368</v>
       </c>
       <c r="N2" t="n">
-        <v>26.79688370677278</v>
+        <v>26.72913278727509</v>
       </c>
       <c r="O2" t="n">
-        <v>5.176570651191073</v>
+        <v>5.170022513227103</v>
       </c>
       <c r="P2" t="n">
-        <v>352.3889137194637</v>
+        <v>352.3951004184643</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -14855,28 +14892,28 @@
         <v>0.0852</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1710736942664515</v>
+        <v>0.1743250188763565</v>
       </c>
       <c r="J3" t="n">
+        <v>378</v>
+      </c>
+      <c r="K3" t="n">
         <v>377</v>
       </c>
-      <c r="K3" t="n">
-        <v>376</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.05702316732935364</v>
+        <v>0.05919756540549392</v>
       </c>
       <c r="M3" t="n">
-        <v>4.033599380284457</v>
+        <v>4.034024730674263</v>
       </c>
       <c r="N3" t="n">
-        <v>26.18474883501023</v>
+        <v>26.21344554045547</v>
       </c>
       <c r="O3" t="n">
-        <v>5.117103559144589</v>
+        <v>5.119906790211661</v>
       </c>
       <c r="P3" t="n">
-        <v>344.4654491648377</v>
+        <v>344.4303953755189</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -14933,28 +14970,28 @@
         <v>0.08119999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2223242357556038</v>
+        <v>0.2279506589921047</v>
       </c>
       <c r="J4" t="n">
+        <v>378</v>
+      </c>
+      <c r="K4" t="n">
         <v>377</v>
       </c>
-      <c r="K4" t="n">
-        <v>376</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.06640341432738595</v>
+        <v>0.06944213821719358</v>
       </c>
       <c r="M4" t="n">
-        <v>4.812921924276665</v>
+        <v>4.828125059786455</v>
       </c>
       <c r="N4" t="n">
-        <v>37.59886357030088</v>
+        <v>37.79306222826153</v>
       </c>
       <c r="O4" t="n">
-        <v>6.131791220377687</v>
+        <v>6.147606219355752</v>
       </c>
       <c r="P4" t="n">
-        <v>345.0135695307458</v>
+        <v>344.9529088836513</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -15011,28 +15048,28 @@
         <v>0.1843</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2282106727152822</v>
+        <v>0.2318295923158165</v>
       </c>
       <c r="J5" t="n">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="K5" t="n">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06259443001717435</v>
+        <v>0.06464182259898388</v>
       </c>
       <c r="M5" t="n">
-        <v>5.304739528806116</v>
+        <v>5.309202655053458</v>
       </c>
       <c r="N5" t="n">
-        <v>42.59741022483987</v>
+        <v>42.60801221963987</v>
       </c>
       <c r="O5" t="n">
-        <v>6.52666915239618</v>
+        <v>6.527481307490651</v>
       </c>
       <c r="P5" t="n">
-        <v>339.8086876688735</v>
+        <v>339.769922372697</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -15089,28 +15126,28 @@
         <v>0.0422</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.151106167928276</v>
+        <v>-0.1437612259197094</v>
       </c>
       <c r="J6" t="n">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="K6" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="L6" t="n">
-        <v>0.003122727866169406</v>
+        <v>0.002840267478800174</v>
       </c>
       <c r="M6" t="n">
-        <v>15.10417033632293</v>
+        <v>15.10827308670319</v>
       </c>
       <c r="N6" t="n">
-        <v>390.4752257664189</v>
+        <v>389.9264310134914</v>
       </c>
       <c r="O6" t="n">
-        <v>19.76044599108074</v>
+        <v>19.74655491506028</v>
       </c>
       <c r="P6" t="n">
-        <v>364.2585776855964</v>
+        <v>364.1786688895991</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -15148,7 +15185,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G378"/>
+  <dimension ref="A1:G379"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29113,6 +29150,43 @@
         </is>
       </c>
     </row>
+    <row r="379">
+      <c r="A379" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-14 22:05:26+00:00</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>-36.76833392064454,175.74969318220778</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>-36.76903515631055,175.7494795371989</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>-36.76975483635323,175.7494101280911</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>-36.77046626875516,175.74920601620386</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>-36.77116157425957,175.74946856433104</t>
+        </is>
+      </c>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0168/nzd0168.xlsx
+++ b/data/nzd0168/nzd0168.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G379"/>
+  <dimension ref="A1:G381"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10659,6 +10659,60 @@
       <c r="G379" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:04:44+00:00</t>
+        </is>
+      </c>
+      <c r="B380" t="n">
+        <v>355.21</v>
+      </c>
+      <c r="C380" t="n">
+        <v>351.37</v>
+      </c>
+      <c r="D380" t="n">
+        <v>358.04</v>
+      </c>
+      <c r="E380" t="n">
+        <v>346.69</v>
+      </c>
+      <c r="F380" t="n">
+        <v>363.19</v>
+      </c>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:05:20+00:00</t>
+        </is>
+      </c>
+      <c r="B381" t="n">
+        <v>354.83</v>
+      </c>
+      <c r="C381" t="n">
+        <v>351.06</v>
+      </c>
+      <c r="D381" t="n">
+        <v>357.75</v>
+      </c>
+      <c r="E381" t="n">
+        <v>348.66</v>
+      </c>
+      <c r="F381" t="n">
+        <v>359.73</v>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -10673,7 +10727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B397"/>
+  <dimension ref="A1:B399"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14646,6 +14700,26 @@
       </c>
       <c r="B397" t="n">
         <v>-0.42</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B398" t="n">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B399" t="n">
+        <v>-0.54</v>
       </c>
     </row>
   </sheetData>
@@ -14814,28 +14888,28 @@
         <v>0.055</v>
       </c>
       <c r="I2" t="n">
-        <v>0.09063973406783112</v>
+        <v>0.09084127389145302</v>
       </c>
       <c r="J2" t="n">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="K2" t="n">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01656109086280277</v>
+        <v>0.01682756216609593</v>
       </c>
       <c r="M2" t="n">
-        <v>3.93009710910368</v>
+        <v>3.910320624590839</v>
       </c>
       <c r="N2" t="n">
-        <v>26.72913278727509</v>
+        <v>26.58883246366461</v>
       </c>
       <c r="O2" t="n">
-        <v>5.170022513227103</v>
+        <v>5.156436023423989</v>
       </c>
       <c r="P2" t="n">
-        <v>352.3951004184643</v>
+        <v>352.3929256337854</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -14892,28 +14966,28 @@
         <v>0.0852</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1743250188763565</v>
+        <v>0.1765637290072525</v>
       </c>
       <c r="J3" t="n">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="K3" t="n">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05919756540549392</v>
+        <v>0.06126304322214393</v>
       </c>
       <c r="M3" t="n">
-        <v>4.034024730674263</v>
+        <v>4.020203507558906</v>
       </c>
       <c r="N3" t="n">
-        <v>26.21344554045547</v>
+        <v>26.09820053606271</v>
       </c>
       <c r="O3" t="n">
-        <v>5.119906790211661</v>
+        <v>5.108639793140902</v>
       </c>
       <c r="P3" t="n">
-        <v>344.4303953755189</v>
+        <v>344.4060722604362</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -14970,28 +15044,28 @@
         <v>0.08119999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2279506589921047</v>
+        <v>0.2352116140117619</v>
       </c>
       <c r="J4" t="n">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="K4" t="n">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="L4" t="n">
-        <v>0.06944213821719358</v>
+        <v>0.07397835142590303</v>
       </c>
       <c r="M4" t="n">
-        <v>4.828125059786455</v>
+        <v>4.838514348885925</v>
       </c>
       <c r="N4" t="n">
-        <v>37.79306222826153</v>
+        <v>37.83521832182485</v>
       </c>
       <c r="O4" t="n">
-        <v>6.147606219355752</v>
+        <v>6.151033922994154</v>
       </c>
       <c r="P4" t="n">
-        <v>344.9529088836513</v>
+        <v>344.874018280026</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -15048,28 +15122,28 @@
         <v>0.1843</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2318295923158165</v>
+        <v>0.2336056737494256</v>
       </c>
       <c r="J5" t="n">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="K5" t="n">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06464182259898388</v>
+        <v>0.06626919179851198</v>
       </c>
       <c r="M5" t="n">
-        <v>5.309202655053458</v>
+        <v>5.290225871775274</v>
       </c>
       <c r="N5" t="n">
-        <v>42.60801221963987</v>
+        <v>42.40344406895075</v>
       </c>
       <c r="O5" t="n">
-        <v>6.527481307490651</v>
+        <v>6.511792692412033</v>
       </c>
       <c r="P5" t="n">
-        <v>339.769922372697</v>
+        <v>339.7507431163783</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -15126,28 +15200,28 @@
         <v>0.0422</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1437612259197094</v>
+        <v>-0.1425406893750845</v>
       </c>
       <c r="J6" t="n">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="K6" t="n">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002840267478800174</v>
+        <v>0.002825483255836758</v>
       </c>
       <c r="M6" t="n">
-        <v>15.10827308670319</v>
+        <v>15.03839852582674</v>
       </c>
       <c r="N6" t="n">
-        <v>389.9264310134914</v>
+        <v>387.8750223688465</v>
       </c>
       <c r="O6" t="n">
-        <v>19.74655491506028</v>
+        <v>19.69454295912567</v>
       </c>
       <c r="P6" t="n">
-        <v>364.1786688895991</v>
+        <v>364.1652964578739</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -15185,7 +15259,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G379"/>
+  <dimension ref="A1:G381"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29187,6 +29261,80 @@
         </is>
       </c>
     </row>
+    <row r="380">
+      <c r="A380" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:04:44+00:00</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>-36.76833705155699,175.7497092899774</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>-36.769028866221554,175.74943816933762</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>-36.76975117578554,175.74937154194546</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>-36.77046487560829,175.7491381840244</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>-36.77116632938818,175.74934878832545</t>
+        </is>
+      </c>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:05:20+00:00</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>-36.76833624767427,175.7497051541986</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>-36.76902834762312,175.74943475868974</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>-36.76975086985855,175.74936831716684</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>-36.77046532850023,175.74916023507942</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>-36.77116786556651,175.74931009317783</t>
+        </is>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0168/nzd0168.xlsx
+++ b/data/nzd0168/nzd0168.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G381"/>
+  <dimension ref="A1:G382"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10711,6 +10711,33 @@
         <v>359.73</v>
       </c>
       <c r="G381" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:05:18+00:00</t>
+        </is>
+      </c>
+      <c r="B382" t="n">
+        <v>354.45</v>
+      </c>
+      <c r="C382" t="n">
+        <v>350.62</v>
+      </c>
+      <c r="D382" t="n">
+        <v>357</v>
+      </c>
+      <c r="E382" t="n">
+        <v>348.66</v>
+      </c>
+      <c r="F382" t="n">
+        <v>356.28</v>
+      </c>
+      <c r="G382" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -10727,7 +10754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B399"/>
+  <dimension ref="A1:B400"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14720,6 +14747,16 @@
       </c>
       <c r="B399" t="n">
         <v>-0.54</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B400" t="n">
+        <v>-0.55</v>
       </c>
     </row>
   </sheetData>
@@ -14888,28 +14925,28 @@
         <v>0.055</v>
       </c>
       <c r="I2" t="n">
-        <v>0.09084127389145302</v>
+        <v>0.09063946059707843</v>
       </c>
       <c r="J2" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="K2" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01682756216609593</v>
+        <v>0.01685073489985345</v>
       </c>
       <c r="M2" t="n">
-        <v>3.910320624590839</v>
+        <v>3.901153563790137</v>
       </c>
       <c r="N2" t="n">
-        <v>26.58883246366461</v>
+        <v>26.519428756305</v>
       </c>
       <c r="O2" t="n">
-        <v>5.156436023423989</v>
+        <v>5.149701812367877</v>
       </c>
       <c r="P2" t="n">
-        <v>352.3929256337854</v>
+        <v>352.3951093193738</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -14966,28 +15003,28 @@
         <v>0.0852</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1765637290072525</v>
+        <v>0.1773391626547616</v>
       </c>
       <c r="J3" t="n">
+        <v>381</v>
+      </c>
+      <c r="K3" t="n">
         <v>380</v>
       </c>
-      <c r="K3" t="n">
-        <v>379</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.06126304322214393</v>
+        <v>0.0620986795070021</v>
       </c>
       <c r="M3" t="n">
-        <v>4.020203507558906</v>
+        <v>4.012186776003776</v>
       </c>
       <c r="N3" t="n">
-        <v>26.09820053606271</v>
+        <v>26.03510165012638</v>
       </c>
       <c r="O3" t="n">
-        <v>5.108639793140902</v>
+        <v>5.102460352626601</v>
       </c>
       <c r="P3" t="n">
-        <v>344.4060722604362</v>
+        <v>344.3976280409665</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -15044,28 +15081,28 @@
         <v>0.08119999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2352116140117619</v>
+        <v>0.2382859502798125</v>
       </c>
       <c r="J4" t="n">
+        <v>381</v>
+      </c>
+      <c r="K4" t="n">
         <v>380</v>
       </c>
-      <c r="K4" t="n">
-        <v>379</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.07397835142590303</v>
+        <v>0.07602752673879387</v>
       </c>
       <c r="M4" t="n">
-        <v>4.838514348885925</v>
+        <v>4.840946682258646</v>
       </c>
       <c r="N4" t="n">
-        <v>37.83521832182485</v>
+        <v>37.82337092391187</v>
       </c>
       <c r="O4" t="n">
-        <v>6.151033922994154</v>
+        <v>6.150070806414498</v>
       </c>
       <c r="P4" t="n">
-        <v>344.874018280026</v>
+        <v>344.8405397609359</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -15122,28 +15159,28 @@
         <v>0.1843</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2336056737494256</v>
+        <v>0.2349867021396545</v>
       </c>
       <c r="J5" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="K5" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06626919179851198</v>
+        <v>0.06734314234202898</v>
       </c>
       <c r="M5" t="n">
-        <v>5.290225871775274</v>
+        <v>5.283264902322767</v>
       </c>
       <c r="N5" t="n">
-        <v>42.40344406895075</v>
+        <v>42.31009598376554</v>
       </c>
       <c r="O5" t="n">
-        <v>6.511792692412033</v>
+        <v>6.504621125305111</v>
       </c>
       <c r="P5" t="n">
-        <v>339.7507431163783</v>
+        <v>339.7357999393083</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -15200,28 +15237,28 @@
         <v>0.0422</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1425406893750845</v>
+        <v>-0.1447083629002766</v>
       </c>
       <c r="J6" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="K6" t="n">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002825483255836758</v>
+        <v>0.002928669805338679</v>
       </c>
       <c r="M6" t="n">
-        <v>15.03839852582674</v>
+        <v>15.00689093477098</v>
       </c>
       <c r="N6" t="n">
-        <v>387.8750223688465</v>
+        <v>386.8892831361396</v>
       </c>
       <c r="O6" t="n">
-        <v>19.69454295912567</v>
+        <v>19.66950134436915</v>
       </c>
       <c r="P6" t="n">
-        <v>364.1652964578739</v>
+        <v>364.1891157629049</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -15259,7 +15296,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G381"/>
+  <dimension ref="A1:G382"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29335,6 +29372,43 @@
         </is>
       </c>
     </row>
+    <row r="382">
+      <c r="A382" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:05:18+00:00</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>-36.76833544379141,175.7497010184199</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>-36.76902761154777,175.74942991777024</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>-36.76975007866767,175.74935997722227</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>-36.77046532850023,175.74916023507942</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>-36.771169397292546,175.74927150986352</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
